--- a/Sajjad data/by_country_and_state/USA/OH.xlsx
+++ b/Sajjad data/by_country_and_state/USA/OH.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="667">
   <si>
     <t>Business Name</t>
   </si>
@@ -743,6 +743,1275 @@
   </si>
   <si>
     <t>2026-10-25T09:48:50.359Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist Cincinnati</t>
+  </si>
+  <si>
+    <t>(513) 993-5393</t>
+  </si>
+  <si>
+    <t>2825 Short Vine St, Cincinnati, OH 45219</t>
+  </si>
+  <si>
+    <t>Cincinnati</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+Cincinnati/data=!4m7!3m6!1s0x8841b335659b4ecd:0x795dbac991eab5b8!8m2!3d39.1321255!4d-84.5095534!16s%2Fg%2F11nn12wp56!19sChIJzU6bZTWzQYgRuLXqkcm6XXk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:11.036Z</t>
+  </si>
+  <si>
+    <t>Dental-One</t>
+  </si>
+  <si>
+    <t>(513) 721-6060</t>
+  </si>
+  <si>
+    <t>5 E Liberty St, Cincinnati, OH 45202</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental-One/data=!4m7!3m6!1s0x8841b3fc6ace247f:0xbb1b83ae1569531c!8m2!3d39.1126565!4d-84.5154116!16s%2Fg%2F1tdlvz3h!19sChIJfyTOavyzQYgRHFNpFa6DG7s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:15.250Z</t>
+  </si>
+  <si>
+    <t>Cincinnati City Dental Clinics</t>
+  </si>
+  <si>
+    <t>(513) 357-2704</t>
+  </si>
+  <si>
+    <t>City government office</t>
+  </si>
+  <si>
+    <t>2136 W 8th St, Cincinnati, OH 45204</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cincinnati+City+Dental+Clinics/data=!4m7!3m6!1s0x8841b69b5f8a2173:0xb5b006a884946507!8m2!3d39.1057566!4d-84.5524397!16s%2Fg%2F1tdlhzvl!19sChIJcyGKX5u2QYgRB2WUhKgGsLU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:17.091Z</t>
+  </si>
+  <si>
+    <t>Crest Smile Shoppe.</t>
+  </si>
+  <si>
+    <t>(513) 352-4072</t>
+  </si>
+  <si>
+    <t>612 Rockdale Ave, Cincinnati, OH 45229</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Crest+Smile+Shoppe./data=!4m7!3m6!1s0x8841b3a6a49f3b6f:0x982744ae594e8fe0!8m2!3d39.1451093!4d-84.4947531!16s%2Fg%2F1q5bmn2qr!19sChIJbzufpKazQYgR4I9OWa5EJ5g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:19.697Z</t>
+  </si>
+  <si>
+    <t>(513) 357-7610</t>
+  </si>
+  <si>
+    <t>3917 Spring Grove Ave, Cincinnati, OH 45223</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cincinnati+City+Dental+Clinics/data=!4m7!3m6!1s0x8841b48c8ed44611:0x4d951edbaac95d32!8m2!3d39.157476!4d-84.5407167!16s%2Fg%2F1tmy5r14!19sChIJEUbUjoy0QYgRMl3JqtselU0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:21.682Z</t>
+  </si>
+  <si>
+    <t>Roselawn Family Dental</t>
+  </si>
+  <si>
+    <t>(513) 821-3118</t>
+  </si>
+  <si>
+    <t>7540 Reading Rd, Cincinnati, OH 45237</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Roselawn+Family+Dental/data=!4m7!3m6!1s0x88404d486eff4083:0x4d8669200231ba9c!8m2!3d39.1986159!4d-84.4575064!16s%2Fg%2F1v62jb9r!19sChIJg0D_bkhNQIgRnLoxAiBphk0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:23.754Z</t>
+  </si>
+  <si>
+    <t>Miller Lloyd DDS</t>
+  </si>
+  <si>
+    <t>(513) 451-3999</t>
+  </si>
+  <si>
+    <t>5928 Glenway Ave, Cincinnati, OH 45238</t>
+  </si>
+  <si>
+    <t>Sunday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Miller+Lloyd+DDS/data=!4m7!3m6!1s0x8841ca71fee07457:0x998b7b922af5ed83!8m2!3d39.1396259!4d-84.6162815!16s%2Fg%2F1twy_70j!19sChIJV3Tg_nHKQYgRg-31KpJ7i5k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:40.222Z</t>
+  </si>
+  <si>
+    <t>Greenhills Family Dentistry</t>
+  </si>
+  <si>
+    <t>(513) 825-2121</t>
+  </si>
+  <si>
+    <t>42 Eswin St, Cincinnati, OH 45218</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Greenhills+Family+Dentistry/data=!4m7!3m6!1s0x88404bf8ab902a69:0x18e8f4aa316c73e6!8m2!3d39.2695737!4d-84.5225393!16s%2Fg%2F1tnjk7gs!19sChIJaSqQq_hLQIgR5nNsMar06Bg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:53.353Z</t>
+  </si>
+  <si>
+    <t>Bateman Dana K DDS</t>
+  </si>
+  <si>
+    <t>(513) 351-7252</t>
+  </si>
+  <si>
+    <t>6526 Montgomery Rd, Cincinnati, OH 45213</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bateman+Dana+K+DDS/data=!4m7!3m6!1s0x884052cab793a19b:0x214b83584f58fa62!8m2!3d39.187693!4d-84.4155091!16s%2Fg%2F1tgdttq9!19sChIJm6GTt8pSQIgRYvpYT1iDSyE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:40:58.553Z</t>
+  </si>
+  <si>
+    <t>Bordlee Family and Cosmetic Dentistry</t>
+  </si>
+  <si>
+    <t>(513) 731-1106</t>
+  </si>
+  <si>
+    <t>6204 Ridge Ave, Cincinnati, OH 45213</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bordlee+Family+and+Cosmetic+Dentistry/data=!4m7!3m6!1s0x8841adcbfc67042d:0xbdd3d96298beb68!8m2!3d39.1849632!4d-84.4271316!16s%2Fg%2F11svqbtnsz!19sChIJLQRn_MutQYgRaOuLKZY93Qs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:00.703Z</t>
+  </si>
+  <si>
+    <t>Wyand Ralph E DDS</t>
+  </si>
+  <si>
+    <t>(513) 321-4286</t>
+  </si>
+  <si>
+    <t>2752 Erie Ave, Cincinnati, OH 45208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Wyand+Ralph+E+DDS/data=!4m7!3m6!1s0x8841b278e2bf45e1:0xd3fad3e22e3c5e74!8m2!3d39.1397429!4d-84.4408563!16s%2Fg%2F1tgx2q2f!19sChIJ4UW_4niyQYgRdF48LuLT-tM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:49.507Z</t>
+  </si>
+  <si>
+    <t>White Travis DDS</t>
+  </si>
+  <si>
+    <t>(859) 539-4036</t>
+  </si>
+  <si>
+    <t>3333 Burnet Ave, Cincinnati, OH 45229</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/White+Travis+DDS/data=!4m7!3m6!1s0x8841b3986f450c5d:0xac0f52511f9157dc!8m2!3d39.1409252!4d-84.501505!16s%2Fg%2F1vh_91bf!19sChIJXQxFb5izQYgR3FeRH1FSD6w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:51.471Z</t>
+  </si>
+  <si>
+    <t>Dr. David M. Rider, DMD</t>
+  </si>
+  <si>
+    <t>(513) 791-6154</t>
+  </si>
+  <si>
+    <t>4157 Hunt Rd, Blue Ash, OH 45236</t>
+  </si>
+  <si>
+    <t>Blue Ash</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+David+M.+Rider,+DMD/data=!4m7!3m6!1s0x884053003cd42587:0x86963ca0835e8942!8m2!3d39.226033!4d-84.3955812!16s%2Fg%2F1w96hdxz!19sChIJhyXUPABTQIgRQoleg6A8loY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:41:55.948Z</t>
+  </si>
+  <si>
+    <t>Dr. David R. Oliver, DDS</t>
+  </si>
+  <si>
+    <t>(513) 231-2100</t>
+  </si>
+  <si>
+    <t>7655 Five Mile Rd, Cincinnati, OH 45230</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+David+R.+Oliver,+DDS/data=!4m7!3m6!1s0x8841a9328d23f355:0x27a9be0674259cc6!8m2!3d39.0708383!4d-84.3514606!16s%2Fg%2F1tkp0gjk!19sChIJVfMjjTKpQYgRxpwldAa-qSc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:02.166Z</t>
+  </si>
+  <si>
+    <t>JP Larson, DDS (Retired) - New owner as of Nov. 2024</t>
+  </si>
+  <si>
+    <t>(513) 528-1223</t>
+  </si>
+  <si>
+    <t>497 Cincinnati-Batavia Pike, Cincinnati, OH 45244</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/JP+Larson,+DDS+%28Retired%29+-+New+owner+as+of+Nov.+2024/data=!4m7!3m6!1s0x8841aa2fa5901a45:0xb9632aedb935c00d!8m2!3d39.1063834!4d-84.303323!16s%2Fg%2F1thl_3hq!19sChIJRRqQpS-qQYgRDcA1ue0qY7k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:42:03.930Z</t>
+  </si>
+  <si>
+    <t>Express Dental Care</t>
+  </si>
+  <si>
+    <t>(513) 506-8097</t>
+  </si>
+  <si>
+    <t>8077 Colerain Ave, Cincinnati, OH 45239</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Express+Dental+Care/data=!4m7!3m6!1s0x88404bbf6a64d399:0x41ba94842fef3d2c!8m2!3d39.2189452!4d-84.5860672!16s%2Fg%2F11wqzrlb1k!19sChIJmdNkar9LQIgRLD3vL4SUukE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:43:45.758Z</t>
+  </si>
+  <si>
+    <t>UrgentDent Solutions</t>
+  </si>
+  <si>
+    <t>(513) 447-8480</t>
+  </si>
+  <si>
+    <t>3060 Warsaw Ave, Cincinnati, OH 45205</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/UrgentDent+Solutions/data=!4m7!3m6!1s0x8841b7dfc36dc8df:0xd4d8fadd6287b42a!8m2!3d39.110149!4d-84.561839!16s%2Fg%2F11w3g7s0q5!19sChIJ38htw9-3QYgRKrSHYt362NQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:43:48.021Z</t>
+  </si>
+  <si>
+    <t>NV Smiles</t>
+  </si>
+  <si>
+    <t>(513) 349-6572</t>
+  </si>
+  <si>
+    <t>12006 Pippin Rd, Cincinnati, OH 45231</t>
+  </si>
+  <si>
+    <t>Sunday11 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/NV+Smiles/data=!4m7!3m6!1s0x884049d2578654a9:0x93816e74871ce619!8m2!3d39.3031858!4d-84.5714609!16s%2Fg%2F11qs3szh8p!19sChIJqVSGV9JJQIgRGeYch3RugZM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:44:56.277Z</t>
+  </si>
+  <si>
+    <t>Blume &amp; Ezis</t>
+  </si>
+  <si>
+    <t>(513) 871-8488</t>
+  </si>
+  <si>
+    <t>4030 Smith Rd #225, Cincinnati, OH 45209</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Blume+%26+Ezis/data=!4m7!3m6!1s0x8841b286a23cc7f7:0x4b0936c3458c91e0!8m2!3d39.1519607!4d-84.4447079!16s%2Fg%2F1tcxkfw9!19sChIJ98c8ooayQYgR4JGMRcM2CUs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:45:08.810Z</t>
+  </si>
+  <si>
+    <t>DENTAL DEFINITIONS.</t>
+  </si>
+  <si>
+    <t>(419) 382-8888</t>
+  </si>
+  <si>
+    <t>5350 Airport Hwy #109, Toledo, OH 43615</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DENTAL+DEFINITIONS./data=!4m7!3m6!1s0x883c79857a6760e1:0x8cc79ebcc6c26d5d!8m2!3d41.6171303!4d-83.668518!16s%2Fg%2F1trplwhs!19sChIJ4WBneoV5PIgRXW3Cxryex4w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:46:35.610Z</t>
+  </si>
+  <si>
+    <t>Dr. Abraham H. Boadi, DMD</t>
+  </si>
+  <si>
+    <t>(419) 534-2479</t>
+  </si>
+  <si>
+    <t>36 S Byrne Rd, Toledo, OH 43615</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Abraham+H.+Boadi,+DMD/data=!4m7!3m6!1s0x883c78e5b9042867:0x553b9a05e5b4eb95!8m2!3d41.6373428!4d-83.6261326!16s%2Fg%2F1wk7rjkd!19sChIJZygEueV4PIgRleu05QWaO1U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:47:09.543Z</t>
+  </si>
+  <si>
+    <t>Forche Family Dentistry: John R Forche DDS</t>
+  </si>
+  <si>
+    <t>(419) 382-0357</t>
+  </si>
+  <si>
+    <t>3409 Winston Blvd, Toledo, OH 43614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Forche+Family+Dentistry:+John+R+Forche+DDS/data=!4m7!3m6!1s0x883c783829c02eab:0x2c4c6ea465069d41!8m2!3d41.6017433!4d-83.6240374!16s%2Fg%2F1thnpftf!19sChIJqy7AKTh4PIgRQZ0GZaRuTCw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:47:16.473Z</t>
+  </si>
+  <si>
+    <t>Armstrong Earl DDS</t>
+  </si>
+  <si>
+    <t>(419) 380-8094</t>
+  </si>
+  <si>
+    <t>3536 Glendale Ave E, Toledo, OH 43614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Armstrong+Earl+DDS/data=!4m7!3m6!1s0x883c784e3566afd7:0x15ed9c2bec3f98d5!8m2!3d41.6128743!4d-83.6269651!16s%2Fg%2F1tdzgn_0!19sChIJ169mNU54PIgR1Zg_7Cuc7RU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:47:22.676Z</t>
+  </si>
+  <si>
+    <t>Kastner Dental</t>
+  </si>
+  <si>
+    <t>(419) 841-7661</t>
+  </si>
+  <si>
+    <t>3231 Central Park West #201, Toledo, OH 43617</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kastner+Dental/data=!4m7!3m6!1s0x883c7c6d7cc37903:0x9002ef6cefab3785!8m2!3d41.6780034!4d-83.7005906!16s%2Fg%2F1vl9s4v1!19sChIJA3nDfG18PIgRhTer72zvApA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:47:47.656Z</t>
+  </si>
+  <si>
+    <t>University of Toledo-Pediatric</t>
+  </si>
+  <si>
+    <t>(419) 251-8050</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>2222 Cherry St # 1100, Toledo, OH 43608</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/University+of+Toledo-Pediatric/data=!4m7!3m6!1s0x883b81338349c9a5:0xb9d6eb5caf6c747b!8m2!3d41.6613029!4d-83.534308!16s%2Fg%2F1tgdp6rp!19sChIJpclJgzOBO4gRe3Rsr1zr1rk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:02.158Z</t>
+  </si>
+  <si>
+    <t>Dr. Rodney W. Owen, DDS</t>
+  </si>
+  <si>
+    <t>(419) 882-7187</t>
+  </si>
+  <si>
+    <t>5860 W Alexis Rd, Sylvania, OH 43560</t>
+  </si>
+  <si>
+    <t>Sylvania</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Rodney+W.+Owen,+DDS/data=!4m7!3m6!1s0x883c7dd09bd40355:0x8f290ff344df32ae!8m2!3d41.7160231!4d-83.6844384!16s%2Fg%2F1tl_md1c!19sChIJVQPUm9B9PIgRrjLfRPMPKY8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:04.037Z</t>
+  </si>
+  <si>
+    <t>Weaver David S DDS</t>
+  </si>
+  <si>
+    <t>(419) 474-3100</t>
+  </si>
+  <si>
+    <t>4841 Monroe St #255, Toledo, OH 43623</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Weaver+David+S+DDS/data=!4m7!3m6!1s0x883c7f02a1b253cf:0xc65ed1c7ca05c5f3!8m2!3d41.6938357!4d-83.6343532!16s%2Fg%2F1tdb4z5d!19sChIJz1OyoQJ_PIgR88UFysfRXsY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:19.944Z</t>
+  </si>
+  <si>
+    <t>Hartkopf Alfred H DDS</t>
+  </si>
+  <si>
+    <t>(419) 475-7166</t>
+  </si>
+  <si>
+    <t>4157 W Sylvania Ave #2, Toledo, OH 43623</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hartkopf+Alfred+H+DDS/data=!4m7!3m6!1s0x883c7efaa2584c09:0x622624f1c7d7074!8m2!3d41.6907308!4d-83.6422198!16s%2Fg%2F1thl_35y!19sChIJCUxYovp-PIgRdHB9HE9iIgY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:23.346Z</t>
+  </si>
+  <si>
+    <t>Northwest Ohio Implant Center</t>
+  </si>
+  <si>
+    <t>(419) 578-8955</t>
+  </si>
+  <si>
+    <t>3349 Executive Pkwy, Toledo, OH 43606</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Northwest+Ohio+Implant+Center/data=!4m7!3m6!1s0x883c7f222bb5d7a1:0xa488f54cb10ecdee!8m2!3d41.6815045!4d-83.6293486!16s%2Fg%2F11ghr137n_!19sChIJode1KyJ_PIgR7s0OsUz1iKQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:36.130Z</t>
+  </si>
+  <si>
+    <t>Denture Center</t>
+  </si>
+  <si>
+    <t>(419) 243-9079</t>
+  </si>
+  <si>
+    <t>3636 Monroe St, Toledo, OH 43606</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denture+Center/data=!4m7!3m6!1s0x883b80af889b633f:0x1d7a13f977027326!8m2!3d41.6712095!4d-83.5834478!16s%2Fg%2F1v3knr47!19sChIJP2ObiK-AO4gRJnMCd_kTeh0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:39.357Z</t>
+  </si>
+  <si>
+    <t>Bruce J Kloster Inc</t>
+  </si>
+  <si>
+    <t>(419) 474-4974</t>
+  </si>
+  <si>
+    <t>4841 Monroe St #256, Toledo, OH 43623</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bruce+J+Kloster+Inc/data=!4m7!3m6!1s0x883c7f02a1b253cf:0xac550b3c88bff13b!8m2!3d41.6938357!4d-83.6343532!16s%2Fg%2F1w4vklyv!19sChIJz1OyoQJ_PIgRO_G_iDwLVaw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:41.360Z</t>
+  </si>
+  <si>
+    <t>James C Moeller Inc</t>
+  </si>
+  <si>
+    <t>(419) 865-1201</t>
+  </si>
+  <si>
+    <t>5445 Southwyck Blvd #105, Toledo, OH 43614</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/James+C+Moeller+Inc/data=!4m7!3m6!1s0x883c79f14204d42f:0x32c0a9c7d790fe65!8m2!3d41.6006132!4d-83.6711335!16s%2Fg%2F1vl5hg14!19sChIJL9QEQvF5PIgRZf6Q18epwDI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:43.750Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Connection</t>
+  </si>
+  <si>
+    <t>(419) 573-1088</t>
+  </si>
+  <si>
+    <t>4022 Talmadge Rd, Toledo, OH 43623</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Connection/data=!4m7!3m6!1s0x883c7f6fb1851539:0x25ab630e3f3ac98e!8m2!3d41.6920014!4d-83.6439093!16s%2Fg%2F11zy8sbps8!19sChIJORWFsW9_PIgRjsk6Pw5jqyU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:48:56.999Z</t>
+  </si>
+  <si>
+    <t>Maumee Valley Dental Care</t>
+  </si>
+  <si>
+    <t>(419) 893-3443</t>
+  </si>
+  <si>
+    <t>1657 Holland Rd, Maumee, OH 43537</t>
+  </si>
+  <si>
+    <t>Maumee</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Maumee+Valley+Dental+Care/data=!4m7!3m6!1s0x883c7a00207ad06b:0x53040c4b4a175320!8m2!3d41.5886438!4d-83.6772321!16s%2Fg%2F1vv2sxpd!19sChIJa9B6IAB6PIgRIFMXSksMBFM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:49:00.279Z</t>
+  </si>
+  <si>
+    <t>North Toledo Dental Center</t>
+  </si>
+  <si>
+    <t>(419) 475-1956</t>
+  </si>
+  <si>
+    <t>4601 Douglas Rd, Toledo, OH 43613</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+Toledo+Dental+Center/data=!4m7!3m6!1s0x883c7f77bfa8f153:0x7ac65eaaf512e232!8m2!3d41.7008569!4d-83.604403!16s%2Fg%2F1vq75jm8!19sChIJU_Gov3d_PIgRMuIS9apexno?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:49:18.794Z</t>
+  </si>
+  <si>
+    <t>Bright Expressions Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(419) 410-6062</t>
+  </si>
+  <si>
+    <t>4334 Central Ave #231, Toledo, OH 43615</t>
+  </si>
+  <si>
+    <t>Sunday8 AM–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+Expressions+Teeth+Whitening/data=!4m7!3m6!1s0x883c7edb2bc38dd5:0x49ad114ca279bd83!8m2!3d41.677398!4d-83.645207!16s%2Fg%2F11cn3d_kt7!19sChIJ1Y3DK9t-PIgRg715okwRrUk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:49:49.832Z</t>
+  </si>
+  <si>
+    <t>Cleveland Dental Institute</t>
+  </si>
+  <si>
+    <t>(330) 773-7100</t>
+  </si>
+  <si>
+    <t>1494 S Arlington St, Akron, OH 44306</t>
+  </si>
+  <si>
+    <t>Akron</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cleveland+Dental+Institute/data=!4m7!3m6!1s0x88312bede3ab11df:0xd11368f02d281600!8m2!3d41.031407!4d-81.492175!16s%2Fg%2F11q8v36ngv!19sChIJ3xGr4-0rMYgRABYoLfBoE9E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:50:17.933Z</t>
+  </si>
+  <si>
+    <t>Kenmore Family Dental</t>
+  </si>
+  <si>
+    <t>(330) 753-8155</t>
+  </si>
+  <si>
+    <t>2383 S Main St Ste C-100, Akron, OH 44319</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kenmore+Family+Dental/data=!4m7!3m6!1s0x8830d5d25779762b:0x8037438eb0907046!8m2!3d41.0222604!4d-81.5258494!16s%2Fg%2F1tdy9qcw!19sChIJK3Z5V9LVMIgRRnCQsI5DN4A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:50:21.285Z</t>
+  </si>
+  <si>
+    <t>Responsive Dental Care</t>
+  </si>
+  <si>
+    <t>(866) 332-1620</t>
+  </si>
+  <si>
+    <t>172 Oakdale Ave, Akron, OH 44302</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Responsive+Dental+Care/data=!4m7!3m6!1s0x8830d70e2d93ff09:0x7eaa84e76e832942!8m2!3d41.0873669!4d-81.5330926!16s%2Fg%2F11nb9bc647!19sChIJCf-TLQ7XMIgRQimDbueEqn4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:50:24.397Z</t>
+  </si>
+  <si>
+    <t>Dental Care Support</t>
+  </si>
+  <si>
+    <t>(330) 295-3067</t>
+  </si>
+  <si>
+    <t>2166 Front St, Cuyahoga Falls, OH 44221</t>
+  </si>
+  <si>
+    <t>Cuyahoga Falls</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Care+Support/data=!4m7!3m6!1s0x883127fc99a2967f:0x95e91891508af559!8m2!3d41.1360894!4d-81.4830089!16s%2Fg%2F11zz0ry7vy!19sChIJf5aimfwnMYgRWfWKUJEY6ZU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:50:28.063Z</t>
+  </si>
+  <si>
+    <t>Akron Sedation Dental Works</t>
+  </si>
+  <si>
+    <t>(330) 935-4180</t>
+  </si>
+  <si>
+    <t>3867 W Market St #239, Akron, OH 44333</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Akron+Sedation+Dental+Works/data=!4m7!3m6!1s0x8830d082e847abdb:0xe3b32b7f6983fb6d!8m2!3d41.1358542!4d-81.6378517!16s%2Fg%2F11cm075h04!19sChIJ26tH6ILQMIgRbfuDaX8rs-M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:50:29.678Z</t>
+  </si>
+  <si>
+    <t>+263 78 278 3556</t>
+  </si>
+  <si>
+    <t>491 W Exchange St, Akron, OH 44302</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Responsive+Dental+Care/data=!4m7!3m6!1s0x8830d7790fa0c293:0x88392cf5a3220fbd!8m2!3d41.0851098!4d-81.53595!16s%2Fg%2F11w4bvq8y7!19sChIJk8KgD3nXMIgRvQ8io_UsOYg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:50:32.405Z</t>
+  </si>
+  <si>
+    <t>Julie Rudgers Croft, DDS, MS</t>
+  </si>
+  <si>
+    <t>(234) 602-2555</t>
+  </si>
+  <si>
+    <t>725 W Streetsboro St, Hudson, OH 44236</t>
+  </si>
+  <si>
+    <t>Hudson</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Julie+Rudgers+Croft,+DDS,+MS/data=!4m7!3m6!1s0x8830d7f75657f3c9:0xa1c9db00fd0789f0!8m2!3d41.2335629!4d-81.483244!16s%2Fg%2F11fn04_02f!19sChIJyfNXVvfXMIgR8IkH_QDbyaE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:52:30.827Z</t>
+  </si>
+  <si>
+    <t>Alireza Null Karbassi</t>
+  </si>
+  <si>
+    <t>(234) 285-3315</t>
+  </si>
+  <si>
+    <t>1180 S Main St Ste 402, Akron, OH 44301</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Alireza+Null+Karbassi/data=!4m7!3m6!1s0x8830d60919685319:0xa0a28635b75ce9ea!8m2!3d41.0531729!4d-81.5299091!16s%2Fg%2F11ty7v18vp!19sChIJGVNoGQnWMIgR6ulctzWGoqA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:52:44.469Z</t>
+  </si>
+  <si>
+    <t>Cosmetic Dentistry Akron, Ohio</t>
+  </si>
+  <si>
+    <t>(888) 678-4536</t>
+  </si>
+  <si>
+    <t>Cosmetic dentist</t>
+  </si>
+  <si>
+    <t>2858 S Arlington Rd, Akron, OH 44312</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cosmetic+Dentistry+Akron,+Ohio/data=!4m7!3m6!1s0x88312aecc2a8aeb7:0x87f28cf7778b8c4c!8m2!3d40.9936214!4d-81.4928248!16s%2Fg%2F1hm20819r!19sChIJt66owuwqMYgRTIyLd_eM8oc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:52:58.023Z</t>
+  </si>
+  <si>
+    <t>Quick Dental Services</t>
+  </si>
+  <si>
+    <t>(330) 299-4675</t>
+  </si>
+  <si>
+    <t>1200 E Market St, Akron, OH 44305</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quick+Dental+Services/data=!4m7!3m6!1s0x883129206393fa5b:0xd7994d9483fb8661!8m2!3d41.0655199!4d-81.4829056!16s%2Fg%2F11zxx7hp02!19sChIJW_qTYyApMYgRYYb7g5RNmdc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:53:11.683Z</t>
+  </si>
+  <si>
+    <t>Bright Dental Choice</t>
+  </si>
+  <si>
+    <t>(330) 368-1723</t>
+  </si>
+  <si>
+    <t>2971 W Market St, Fairlawn, OH 44333</t>
+  </si>
+  <si>
+    <t>Fairlawn</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bright+Dental+Choice/data=!4m7!3m6!1s0x8830d1d91e23ba1f:0x6ae67e04a42f942e!8m2!3d41.1283415!4d-81.6089559!16s%2Fg%2F11w9c1mfht!19sChIJH7ojHtnRMIgRLpQvpAR-5mo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:53:18.483Z</t>
+  </si>
+  <si>
+    <t>Jeffrey Rosenthal</t>
+  </si>
+  <si>
+    <t>(330) 535-7876</t>
+  </si>
+  <si>
+    <t>1180 S Main St, Akron, OH 44301</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jeffrey+Rosenthal/data=!4m7!3m6!1s0x8830d60919685319:0xade383bbe740b24b!8m2!3d41.0531729!4d-81.5299091!16s%2Fg%2F11sd2y9428!19sChIJGVNoGQnWMIgRS7JA57uD460?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:53:20.575Z</t>
+  </si>
+  <si>
+    <t>Bruce Imbeau, D.D.S: The Confi-Dent Smile</t>
+  </si>
+  <si>
+    <t>(330) 645-9180</t>
+  </si>
+  <si>
+    <t>3235 Manchester Rd Ste 2, Akron, OH 44319</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Bruce+Imbeau,+D.D.S:+The+Confi-Dent+Smile/data=!4m7!3m6!1s0x8830d5a9e3b5e43d:0x67c9fd3d446c78ce!8m2!3d41.0119098!4d-81.5524427!16s%2Fg%2F1tf3z_vr!19sChIJPeS146nVMIgRznhsRD39yWc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:53:58.112Z</t>
+  </si>
+  <si>
+    <t>Dr. Pamela S. Amundson, DDS</t>
+  </si>
+  <si>
+    <t>(330) 928-1417</t>
+  </si>
+  <si>
+    <t>555 Graham Rd #100, Cuyahoga Falls, OH 44221</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Pamela+S.+Amundson,+DDS/data=!4m7!3m6!1s0x8830d0aedc7ef7e7:0x8780268b8792866c!8m2!3d41.1595088!4d-81.4920038!16s%2Fg%2F1tgfd_yx!19sChIJ5_d-3K7QMIgRbIaSh4smgIc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:06.409Z</t>
+  </si>
+  <si>
+    <t>Locaffaro, Joseph</t>
+  </si>
+  <si>
+    <t>(330) 928-5551</t>
+  </si>
+  <si>
+    <t>727 Graham Rd, Cuyahoga Falls, OH 44221</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Locaffaro,+Joseph/data=!4m7!3m6!1s0x883127a6bfbc62bb:0xf826696440a6c314!8m2!3d41.1624739!4d-81.4869495!16s%2Fg%2F1w96hcyg!19sChIJu2K8v6YnMYgRFMOmQGRpJvg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:09.740Z</t>
+  </si>
+  <si>
+    <t>Belmont Family Dental</t>
+  </si>
+  <si>
+    <t>(937) 256-7277</t>
+  </si>
+  <si>
+    <t>1585 S Smithville Rd, Dayton, OH 45410</t>
+  </si>
+  <si>
+    <t>Dayton</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Belmont+Family+Dental/data=!4m7!3m6!1s0x88408516c161dc07:0x93eb476ddee3da1!8m2!3d39.7448757!4d-84.1400603!16s%2Fg%2F11md30kyhk!19sChIJB9xhwRaFQIgRoT3u3Xa0Pgk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:26.395Z</t>
+  </si>
+  <si>
+    <t>J. W. DENTAL CLAIMS SUPPORT, LLC</t>
+  </si>
+  <si>
+    <t>(380) 272-5818</t>
+  </si>
+  <si>
+    <t>401 W Hudson Ave, Dayton, OH 45406</t>
+  </si>
+  <si>
+    <t>Sunday7 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/J.+W.+DENTAL+CLAIMS+SUPPORT,+LLC/data=!4m7!3m6!1s0x8840819f5184bc15:0xd41deee86b889727!8m2!3d39.7833013!4d-84.2194651!16s%2Fg%2F11n4fd032n!19sChIJFbyEUZ-BQIgRJ5eIa-juHdQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:30.583Z</t>
+  </si>
+  <si>
+    <t>Clayton Family Dental</t>
+  </si>
+  <si>
+    <t>(937) 890-1102</t>
+  </si>
+  <si>
+    <t>8459 N Main St #120, Dayton, OH 45415</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clayton+Family+Dental/data=!4m7!3m6!1s0x883f7f00174351b9:0x669c1f25fb251217!8m2!3d39.8474652!4d-84.2674912!16s%2Fg%2F11wjmk_f0v!19sChIJuVFDFwB_P4gRFxIl-yUfnGY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:34.020Z</t>
+  </si>
+  <si>
+    <t>Brite White Dental</t>
+  </si>
+  <si>
+    <t>(937) 233-6500</t>
+  </si>
+  <si>
+    <t>7212 Taylorsville Rd, Dayton, OH 45424</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brite+White+Dental/data=!4m7!3m6!1s0x883f7d323bd80ead:0x823490ce1037dae8!8m2!3d39.8604119!4d-84.1058024!16s%2Fg%2F1tx47qr0!19sChIJrQ7YOzJ9P4gR6No3EM6QNII?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:35.967Z</t>
+  </si>
+  <si>
+    <t>Michael L. Ortman, D.D.S.</t>
+  </si>
+  <si>
+    <t>(937) 276-3172</t>
+  </si>
+  <si>
+    <t>4224 Philadelphia Dr, Dayton, OH 45405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michael+L.+Ortman,+D.D.S./data=!4m7!3m6!1s0x88408051155a4c17:0xcbcb7337f205b958!8m2!3d39.803586!4d-84.2346983!16s%2Fg%2F1tdg8gyv!19sChIJF0xaFVGAQIgRWLkF8jdzy8s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:48.641Z</t>
+  </si>
+  <si>
+    <t>Dr. Truman L. Martin, DDS</t>
+  </si>
+  <si>
+    <t>(937) 278-9126</t>
+  </si>
+  <si>
+    <t>3740 Salem Ave, Dayton, OH 45406</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Truman+L.+Martin,+DDS/data=!4m7!3m6!1s0x8840808ad6a2ef03:0x6909cfc8c0953192!8m2!3d39.7956683!4d-84.2493209!16s%2Fg%2F1tcy9l45!19sChIJA--i1oqAQIgRkjGVwMjPCWk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:54:50.749Z</t>
+  </si>
+  <si>
+    <t>Dr. Rodney C. Robbins, DDS</t>
+  </si>
+  <si>
+    <t>(937) 433-4060</t>
+  </si>
+  <si>
+    <t>7265 Far Hills Ave, Washington Township, OH 45459</t>
+  </si>
+  <si>
+    <t>Washington Township</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Rodney+C.+Robbins,+DDS/data=!4m7!3m6!1s0x88408eeb525f442f:0xcee542af9e8c7c37!8m2!3d39.639773!4d-84.1583833!16s%2Fg%2F1t_tkzqy!19sChIJL0RfUuuOQIgRN3yMnq9C5c4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:55:06.048Z</t>
+  </si>
+  <si>
+    <t>The Ohio Periodontal And Dental Implant Center</t>
+  </si>
+  <si>
+    <t>(937) 259-0072</t>
+  </si>
+  <si>
+    <t>4300 Linden Ave, Dayton, OH 45432</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Ohio+Periodontal+And+Dental+Implant+Center/data=!4m7!3m6!1s0x884084a3926ceae3:0xf7a0386ac301c8e1!8m2!3d39.743538!4d-84.1179233!16s%2Fg%2F1hbpws87f!19sChIJ4-pskqOEQIgR4cgBw2o4oPc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:24.400Z</t>
+  </si>
+  <si>
+    <t>Rainbow Dental for Kids</t>
+  </si>
+  <si>
+    <t>(937) 890-4820</t>
+  </si>
+  <si>
+    <t>6830 N Dixie Dr, Dayton, OH 45414</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rainbow+Dental+for+Kids/data=!4m7!3m6!1s0x884081e49db306af:0xace3ba9c37fbdda3!8m2!3d39.8311323!4d-84.1980058!16s%2Fg%2F11h5617yr4!19sChIJrwazneSBQIgRo937N5y646w?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:42.619Z</t>
+  </si>
+  <si>
+    <t>Daniel A Reichert DDS.</t>
+  </si>
+  <si>
+    <t>(937) 293-8272</t>
+  </si>
+  <si>
+    <t>924 Shroyer Rd, Dayton, OH 45419</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Daniel+A+Reichert+DDS./data=!4m7!3m6!1s0x88408446200466ef:0xd54175145bbeae99!8m2!3d39.7216662!4d-84.1607008!16s%2Fg%2F1tgq7b53!19sChIJ72YEIEaEQIgRma6-WxR1QdU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:44.323Z</t>
+  </si>
+  <si>
+    <t>Lee Major K III</t>
+  </si>
+  <si>
+    <t>(937) 837-2722</t>
+  </si>
+  <si>
+    <t>6000 Sycamore Woods Blvd, Dayton, OH 45426</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lee+Major+K+III/data=!4m7!3m6!1s0x88407f0f8523e42d:0x42814bc68a61c764!8m2!3d39.8125953!4d-84.3211746!16s%2Fg%2F1tj4zcxb!19sChIJLeQjhQ9_QIgRZMdhisZLgUI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:46.741Z</t>
+  </si>
+  <si>
+    <t>Marwa Abdelrahman DDS, MSD</t>
+  </si>
+  <si>
+    <t>(937) 426-2653</t>
+  </si>
+  <si>
+    <t>3300 Kemp Rd, Beavercreek, OH 454314200</t>
+  </si>
+  <si>
+    <t>Beavercreek</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marwa+Abdelrahman+DDS,+MSD/data=!4m7!3m6!1s0x88409c7ce7a56121:0xe9360c2e56931d40!8m2!3d39.7559831!4d-84.0558561!16s%2Fg%2F11sh2clmfj!19sChIJIWGl53ycQIgRQB2TVi4MNuk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:48.892Z</t>
+  </si>
+  <si>
+    <t>Kids Love To Smile</t>
+  </si>
+  <si>
+    <t>(937) 836-1206</t>
+  </si>
+  <si>
+    <t>120 W Wenger Rd #1, Englewood, OH 45322</t>
+  </si>
+  <si>
+    <t>Englewood</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kids+Love+To+Smile/data=!4m7!3m6!1s0x883f803fdc38f22f:0x5c90d9ce4f2f3b8d!8m2!3d39.8618609!4d-84.28956!16s%2Fg%2F119ttr1t9!19sChIJL_I43D-AP4gRjTsvT87ZkFw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:50.955Z</t>
+  </si>
+  <si>
+    <t>Pediatric Dentistry of Beavercreek</t>
+  </si>
+  <si>
+    <t>(937) 519-3391</t>
+  </si>
+  <si>
+    <t>3223 Beaver Vu Dr, Beavercreek, OH 45434</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pediatric+Dentistry+of+Beavercreek/data=!4m7!3m6!1s0x88409ba1a76eb509:0xfd68aafb6c1de2f4!8m2!3d39.7241683!4d-84.0555559!16s%2Fg%2F1thmg1_s!19sChIJCbVup6GbQIgR9OIdbPuqaP0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:56:53.046Z</t>
+  </si>
+  <si>
+    <t>Dr. Helen R. Holte, DDS</t>
+  </si>
+  <si>
+    <t>(937) 431-9000</t>
+  </si>
+  <si>
+    <t>2234 Salem Ave #5627, Dayton, OH 45406</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Helen+R.+Holte,+DDS/data=!4m7!3m6!1s0x88409c6378f6ab65:0x85390cb49dfc6e0!8m2!3d39.7840992!4d-84.2287499!16s%2Fg%2F1v3knrf1!19sChIJZav2eGOcQIgR4MbfScuQUwg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:57:06.784Z</t>
+  </si>
+  <si>
+    <t>Ameriplan</t>
+  </si>
+  <si>
+    <t>(937) 274-6915</t>
+  </si>
+  <si>
+    <t>244 W Hillcrest Ave, Dayton, OH 45405</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ameriplan/data=!4m7!3m6!1s0x88408105d2cfa43b:0xd10205f17a2a8d99!8m2!3d39.7908214!4d-84.2199413!16s%2Fg%2F1txy3067!19sChIJO6TP0gWBQIgRmY0qevEFAtE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:05.705Z</t>
+  </si>
+  <si>
+    <t>CHOICE DENTAL OFFICE</t>
+  </si>
+  <si>
+    <t>(937) 960-7585</t>
+  </si>
+  <si>
+    <t>4029 Executive Dr, Beavercreek, OH 45430</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/CHOICE+DENTAL+OFFICE/data=!4m7!3m6!1s0x88409bf49b27bddd:0x7414a8936ab427b1!8m2!3d39.7315605!4d-84.0857232!16s%2Fg%2F11lf4xkfh8!19sChIJ3b0nm_SbQIgRsSe0apOoFHQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:07.307Z</t>
+  </si>
+  <si>
+    <t>Dr. Gary H. Ensor, DDS</t>
+  </si>
+  <si>
+    <t>(937) 208-2204</t>
+  </si>
+  <si>
+    <t>1 Wyoming St, Dayton, OH 45409</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gary+H.+Ensor,+DDS/data=!4m7!3m6!1s0x884086a876e5f699:0x85706025363d9f2b!8m2!3d39.7451432!4d-84.1862548!16s%2Fg%2F1tk705f3!19sChIJmfbldqiGQIgRK589NiVgcIU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:09.341Z</t>
+  </si>
+  <si>
+    <t>Dr. Emer J. Makapugay, DDS</t>
+  </si>
+  <si>
+    <t>(937) 237-9396</t>
+  </si>
+  <si>
+    <t>5399 Brandt Pike, Dayton, OH 45424</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Emer+J.+Makapugay,+DDS/data=!4m7!3m6!1s0x884082a021c2fbed:0x2043104265f01e44!8m2!3d39.8312651!4d-84.1221488!16s%2Fg%2F1tlbpv2c!19sChIJ7fvCIaCCQIgRRB7wZUIQQyA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:11.522Z</t>
+  </si>
+  <si>
+    <t>Dental Care Ultra</t>
+  </si>
+  <si>
+    <t>(937) 612-8260</t>
+  </si>
+  <si>
+    <t>463 Miamisburg Centerville Rd, Washington Township, OH 45459</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Care+Ultra/data=!4m7!3m6!1s0x88408f8e01530c05:0xe6c15d7b98d68123!8m2!3d39.6288974!4d-84.1713935!16s%2Fg%2F11wg8bykzp!19sChIJBQxTAY6PQIgRI4HWmHtdweY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:13.329Z</t>
+  </si>
+  <si>
+    <t>Angel Dental Solutions</t>
+  </si>
+  <si>
+    <t>(937) 980-0625</t>
+  </si>
+  <si>
+    <t>224 N St Clair St, Dayton, OH 45402</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Angel+Dental+Solutions/data=!4m7!3m6!1s0x88408199f28eab0f:0x20b5dee231a6ccaf!8m2!3d39.7638019!4d-84.1889525!16s%2Fg%2F11y573v3jy!19sChIJD6uO8pmBQIgRr8ymMeLetSA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:15.193Z</t>
+  </si>
+  <si>
+    <t>Niemiec David a DDS</t>
+  </si>
+  <si>
+    <t>(937) 890-8901</t>
+  </si>
+  <si>
+    <t>7420 Miller Ln, Dayton, OH 45414</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Niemiec+David+a+DDS/data=!4m7!3m6!1s0x883f7e0b668705c5:0x6e680c55fa963f1f!8m2!3d39.8549045!4d-84.1906171!16s%2Fg%2F1tzzw5c8!19sChIJxQWHZgt-P4gRHz-W-lUMaG4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:17.597Z</t>
+  </si>
+  <si>
+    <t>Total Care Dental</t>
+  </si>
+  <si>
+    <t>(937) 253-8958</t>
+  </si>
+  <si>
+    <t>2317 Woodman Dr, Dayton, OH 45420</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Total+Care+Dental/data=!4m7!3m6!1s0x884084e0dc4e412b:0x9ff8d677a7ae722a!8m2!3d39.713818!4d-84.124319!16s%2Fg%2F125_yly9f!19sChIJK0FO3OCEQIgRKnKup3fW-J8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:20.048Z</t>
+  </si>
+  <si>
+    <t>Dr. Alan D. Janoff, DDS</t>
+  </si>
+  <si>
+    <t>(937) 275-7448</t>
+  </si>
+  <si>
+    <t>1203 Salem Ave, Dayton, OH 45406</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alan+D.+Janoff,+DDS/data=!4m7!3m6!1s0x88408118072eb2d7:0xdd651cb94943fa00!8m2!3d39.7761393!4d-84.2173706!16s%2Fg%2F1v940r51!19sChIJ17IuBxiBQIgRAPpDSbkcZd0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:58:22.704Z</t>
+  </si>
+  <si>
+    <t>Dr. Rupa Hamal</t>
+  </si>
+  <si>
+    <t>(937) 667-2417</t>
+  </si>
+  <si>
+    <t>110 S Tippecanoe Dr, Tipp City, OH 45371</t>
+  </si>
+  <si>
+    <t>Tipp City</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Rupa+Hamal/data=!4m7!3m6!1s0x883f7bd5486b145d:0x568cc08f41712975!8m2!3d39.9578474!4d-84.1838643!16s%2Fg%2F1tdqc7hf!19sChIJXRRrSNV7P4gRdSlxQY_AjFY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:59:23.115Z</t>
+  </si>
+  <si>
+    <t>Douglas Patton, DDS</t>
+  </si>
+  <si>
+    <t>(937) 435-0324</t>
+  </si>
+  <si>
+    <t>5660 Far Hills Ave, Dayton, OH 45429</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Douglas+Patton,+DDS/data=!4m7!3m6!1s0x88408f66a6142207:0xeac89a02b6c80cb0!8m2!3d39.6644428!4d-84.1590229!16s%2Fg%2F1tfmcxy9!19sChIJByIUpmaPQIgRsAzItgKayOo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:59:25.223Z</t>
+  </si>
+  <si>
+    <t>Gary L Porter DDS</t>
+  </si>
+  <si>
+    <t>(937) 298-9911</t>
+  </si>
+  <si>
+    <t>6450 Centerville Business Pkwy, Centerville, OH 45459</t>
+  </si>
+  <si>
+    <t>Centerville</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gary+L+Porter+DDS/data=!4m7!3m6!1s0x884086299c08f057:0x354a802155132c5c!8m2!3d39.6501556!4d-84.1343413!16s%2Fg%2F1tj58fv7!19sChIJV_AInCmGQIgRXCwTVSGASjU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T15:59:27.370Z</t>
   </si>
 </sst>
 </file>
@@ -1123,7 +2392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -2657,6 +3926,3204 @@
         <v>243</v>
       </c>
     </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>244</v>
+      </c>
+      <c r="B38" t="s">
+        <v>245</v>
+      </c>
+      <c r="C38" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" t="s">
+        <v>246</v>
+      </c>
+      <c r="E38" t="s">
+        <v>247</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>248</v>
+      </c>
+      <c r="I38" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" t="s">
+        <v>38</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>249</v>
+      </c>
+      <c r="M38" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>251</v>
+      </c>
+      <c r="B39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" t="s">
+        <v>15</v>
+      </c>
+      <c r="D39" t="s">
+        <v>253</v>
+      </c>
+      <c r="E39" t="s">
+        <v>247</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>254</v>
+      </c>
+      <c r="I39" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" t="s">
+        <v>38</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>255</v>
+      </c>
+      <c r="M39" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>257</v>
+      </c>
+      <c r="B40" t="s">
+        <v>258</v>
+      </c>
+      <c r="C40" t="s">
+        <v>259</v>
+      </c>
+      <c r="D40" t="s">
+        <v>260</v>
+      </c>
+      <c r="E40" t="s">
+        <v>247</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>261</v>
+      </c>
+      <c r="I40" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" t="s">
+        <v>30</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>262</v>
+      </c>
+      <c r="M40" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>264</v>
+      </c>
+      <c r="B41" t="s">
+        <v>265</v>
+      </c>
+      <c r="C41" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" t="s">
+        <v>266</v>
+      </c>
+      <c r="E41" t="s">
+        <v>247</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>267</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>30</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>268</v>
+      </c>
+      <c r="M41" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>257</v>
+      </c>
+      <c r="B42" t="s">
+        <v>270</v>
+      </c>
+      <c r="C42" t="s">
+        <v>259</v>
+      </c>
+      <c r="D42" t="s">
+        <v>271</v>
+      </c>
+      <c r="E42" t="s">
+        <v>247</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>38</v>
+      </c>
+      <c r="I42" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" t="s">
+        <v>38</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>272</v>
+      </c>
+      <c r="M42" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>274</v>
+      </c>
+      <c r="B43" t="s">
+        <v>275</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>276</v>
+      </c>
+      <c r="E43" t="s">
+        <v>247</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>277</v>
+      </c>
+      <c r="M43" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>279</v>
+      </c>
+      <c r="B44" t="s">
+        <v>280</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>281</v>
+      </c>
+      <c r="E44" t="s">
+        <v>247</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>282</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>283</v>
+      </c>
+      <c r="M44" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>285</v>
+      </c>
+      <c r="B45" t="s">
+        <v>286</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>287</v>
+      </c>
+      <c r="E45" t="s">
+        <v>247</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>288</v>
+      </c>
+      <c r="M45" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>290</v>
+      </c>
+      <c r="B46" t="s">
+        <v>291</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>292</v>
+      </c>
+      <c r="E46" t="s">
+        <v>247</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>293</v>
+      </c>
+      <c r="M46" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>295</v>
+      </c>
+      <c r="B47" t="s">
+        <v>296</v>
+      </c>
+      <c r="C47" t="s">
+        <v>15</v>
+      </c>
+      <c r="D47" t="s">
+        <v>297</v>
+      </c>
+      <c r="E47" t="s">
+        <v>247</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>30</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>298</v>
+      </c>
+      <c r="M47" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>300</v>
+      </c>
+      <c r="B48" t="s">
+        <v>301</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
+        <v>302</v>
+      </c>
+      <c r="E48" t="s">
+        <v>247</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>38</v>
+      </c>
+      <c r="I48" t="s">
+        <v>61</v>
+      </c>
+      <c r="J48" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>303</v>
+      </c>
+      <c r="M48" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>305</v>
+      </c>
+      <c r="B49" t="s">
+        <v>306</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" t="s">
+        <v>307</v>
+      </c>
+      <c r="E49" t="s">
+        <v>247</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>38</v>
+      </c>
+      <c r="I49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>308</v>
+      </c>
+      <c r="M49" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>310</v>
+      </c>
+      <c r="B50" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" t="s">
+        <v>312</v>
+      </c>
+      <c r="E50" t="s">
+        <v>313</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>37</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>38</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>314</v>
+      </c>
+      <c r="M50" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>316</v>
+      </c>
+      <c r="B51" t="s">
+        <v>317</v>
+      </c>
+      <c r="C51" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" t="s">
+        <v>318</v>
+      </c>
+      <c r="E51" t="s">
+        <v>247</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>102</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>319</v>
+      </c>
+      <c r="M51" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>321</v>
+      </c>
+      <c r="B52" t="s">
+        <v>322</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>323</v>
+      </c>
+      <c r="E52" t="s">
+        <v>247</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>30</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>324</v>
+      </c>
+      <c r="M52" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>326</v>
+      </c>
+      <c r="B53" t="s">
+        <v>327</v>
+      </c>
+      <c r="C53" t="s">
+        <v>49</v>
+      </c>
+      <c r="D53" t="s">
+        <v>328</v>
+      </c>
+      <c r="E53" t="s">
+        <v>247</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>38</v>
+      </c>
+      <c r="I53" t="s">
+        <v>61</v>
+      </c>
+      <c r="J53" t="s">
+        <v>38</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>329</v>
+      </c>
+      <c r="M53" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>331</v>
+      </c>
+      <c r="B54" t="s">
+        <v>332</v>
+      </c>
+      <c r="C54" t="s">
+        <v>49</v>
+      </c>
+      <c r="D54" t="s">
+        <v>333</v>
+      </c>
+      <c r="E54" t="s">
+        <v>247</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>38</v>
+      </c>
+      <c r="I54" t="s">
+        <v>61</v>
+      </c>
+      <c r="J54" t="s">
+        <v>38</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>334</v>
+      </c>
+      <c r="M54" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>336</v>
+      </c>
+      <c r="B55" t="s">
+        <v>337</v>
+      </c>
+      <c r="C55" t="s">
+        <v>80</v>
+      </c>
+      <c r="D55" t="s">
+        <v>338</v>
+      </c>
+      <c r="E55" t="s">
+        <v>247</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>37</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>339</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>340</v>
+      </c>
+      <c r="M55" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>342</v>
+      </c>
+      <c r="B56" t="s">
+        <v>343</v>
+      </c>
+      <c r="C56" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" t="s">
+        <v>344</v>
+      </c>
+      <c r="E56" t="s">
+        <v>247</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>38</v>
+      </c>
+      <c r="I56" t="s">
+        <v>345</v>
+      </c>
+      <c r="J56" t="s">
+        <v>38</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>346</v>
+      </c>
+      <c r="M56" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>348</v>
+      </c>
+      <c r="B57" t="s">
+        <v>349</v>
+      </c>
+      <c r="C57" t="s">
+        <v>15</v>
+      </c>
+      <c r="D57" t="s">
+        <v>350</v>
+      </c>
+      <c r="E57" t="s">
+        <v>351</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>267</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>30</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>352</v>
+      </c>
+      <c r="M57" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>354</v>
+      </c>
+      <c r="B58" t="s">
+        <v>355</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>356</v>
+      </c>
+      <c r="E58" t="s">
+        <v>351</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>267</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>38</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>357</v>
+      </c>
+      <c r="M58" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>359</v>
+      </c>
+      <c r="B59" t="s">
+        <v>360</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>361</v>
+      </c>
+      <c r="E59" t="s">
+        <v>351</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>254</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>30</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>362</v>
+      </c>
+      <c r="M59" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>364</v>
+      </c>
+      <c r="B60" t="s">
+        <v>365</v>
+      </c>
+      <c r="C60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D60" t="s">
+        <v>366</v>
+      </c>
+      <c r="E60" t="s">
+        <v>351</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>130</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>38</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>367</v>
+      </c>
+      <c r="M60" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>369</v>
+      </c>
+      <c r="B61" t="s">
+        <v>370</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>371</v>
+      </c>
+      <c r="E61" t="s">
+        <v>351</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>372</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>373</v>
+      </c>
+      <c r="M61" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>375</v>
+      </c>
+      <c r="B62" t="s">
+        <v>376</v>
+      </c>
+      <c r="C62" t="s">
+        <v>377</v>
+      </c>
+      <c r="D62" t="s">
+        <v>378</v>
+      </c>
+      <c r="E62" t="s">
+        <v>351</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>38</v>
+      </c>
+      <c r="I62" t="s">
+        <v>61</v>
+      </c>
+      <c r="J62" t="s">
+        <v>38</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>379</v>
+      </c>
+      <c r="M62" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>381</v>
+      </c>
+      <c r="B63" t="s">
+        <v>382</v>
+      </c>
+      <c r="C63" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" t="s">
+        <v>383</v>
+      </c>
+      <c r="E63" t="s">
+        <v>384</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>38</v>
+      </c>
+      <c r="I63" t="s">
+        <v>61</v>
+      </c>
+      <c r="J63" t="s">
+        <v>38</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>385</v>
+      </c>
+      <c r="M63" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>387</v>
+      </c>
+      <c r="B64" t="s">
+        <v>388</v>
+      </c>
+      <c r="C64" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" t="s">
+        <v>389</v>
+      </c>
+      <c r="E64" t="s">
+        <v>351</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>390</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>282</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>391</v>
+      </c>
+      <c r="M64" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>393</v>
+      </c>
+      <c r="B65" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>395</v>
+      </c>
+      <c r="E65" t="s">
+        <v>351</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s">
+        <v>30</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>396</v>
+      </c>
+      <c r="M65" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>398</v>
+      </c>
+      <c r="B66" t="s">
+        <v>399</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>400</v>
+      </c>
+      <c r="E66" t="s">
+        <v>351</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>38</v>
+      </c>
+      <c r="I66" t="s">
+        <v>61</v>
+      </c>
+      <c r="J66" t="s">
+        <v>38</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>401</v>
+      </c>
+      <c r="M66" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>403</v>
+      </c>
+      <c r="B67" t="s">
+        <v>404</v>
+      </c>
+      <c r="C67" t="s">
+        <v>119</v>
+      </c>
+      <c r="D67" t="s">
+        <v>405</v>
+      </c>
+      <c r="E67" t="s">
+        <v>351</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>130</v>
+      </c>
+      <c r="I67" t="s">
+        <v>406</v>
+      </c>
+      <c r="J67" t="s">
+        <v>38</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>407</v>
+      </c>
+      <c r="M67" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>409</v>
+      </c>
+      <c r="B68" t="s">
+        <v>410</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>411</v>
+      </c>
+      <c r="E68" t="s">
+        <v>351</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>169</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>412</v>
+      </c>
+      <c r="M68" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>414</v>
+      </c>
+      <c r="B69" t="s">
+        <v>415</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>416</v>
+      </c>
+      <c r="E69" t="s">
+        <v>351</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s">
+        <v>30</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>417</v>
+      </c>
+      <c r="M69" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>419</v>
+      </c>
+      <c r="B70" t="s">
+        <v>420</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" t="s">
+        <v>421</v>
+      </c>
+      <c r="E70" t="s">
+        <v>351</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>38</v>
+      </c>
+      <c r="I70" t="s">
+        <v>61</v>
+      </c>
+      <c r="J70" t="s">
+        <v>38</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>422</v>
+      </c>
+      <c r="M70" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>424</v>
+      </c>
+      <c r="B71" t="s">
+        <v>425</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>426</v>
+      </c>
+      <c r="E71" t="s">
+        <v>427</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>37</v>
+      </c>
+      <c r="I71" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s">
+        <v>38</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>428</v>
+      </c>
+      <c r="M71" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>430</v>
+      </c>
+      <c r="B72" t="s">
+        <v>431</v>
+      </c>
+      <c r="C72" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" t="s">
+        <v>432</v>
+      </c>
+      <c r="E72" t="s">
+        <v>351</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>37</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>38</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>433</v>
+      </c>
+      <c r="M72" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>435</v>
+      </c>
+      <c r="B73" t="s">
+        <v>436</v>
+      </c>
+      <c r="C73" t="s">
+        <v>80</v>
+      </c>
+      <c r="D73" t="s">
+        <v>437</v>
+      </c>
+      <c r="E73" t="s">
+        <v>351</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>38</v>
+      </c>
+      <c r="I73" t="s">
+        <v>61</v>
+      </c>
+      <c r="J73" t="s">
+        <v>438</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>439</v>
+      </c>
+      <c r="M73" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>441</v>
+      </c>
+      <c r="B74" t="s">
+        <v>442</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>443</v>
+      </c>
+      <c r="E74" t="s">
+        <v>444</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>141</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>114</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>445</v>
+      </c>
+      <c r="M74" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>447</v>
+      </c>
+      <c r="B75" t="s">
+        <v>448</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>449</v>
+      </c>
+      <c r="E75" t="s">
+        <v>444</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>450</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>30</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>451</v>
+      </c>
+      <c r="M75" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>453</v>
+      </c>
+      <c r="B76" t="s">
+        <v>454</v>
+      </c>
+      <c r="C76" t="s">
+        <v>49</v>
+      </c>
+      <c r="D76" t="s">
+        <v>455</v>
+      </c>
+      <c r="E76" t="s">
+        <v>444</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>38</v>
+      </c>
+      <c r="I76" t="s">
+        <v>61</v>
+      </c>
+      <c r="J76" t="s">
+        <v>38</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>456</v>
+      </c>
+      <c r="M76" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>458</v>
+      </c>
+      <c r="B77" t="s">
+        <v>459</v>
+      </c>
+      <c r="C77" t="s">
+        <v>49</v>
+      </c>
+      <c r="D77" t="s">
+        <v>460</v>
+      </c>
+      <c r="E77" t="s">
+        <v>461</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>37</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>38</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>462</v>
+      </c>
+      <c r="M77" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>464</v>
+      </c>
+      <c r="B78" t="s">
+        <v>465</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>466</v>
+      </c>
+      <c r="E78" t="s">
+        <v>444</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>37</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>30</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>467</v>
+      </c>
+      <c r="M78" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>453</v>
+      </c>
+      <c r="B79" t="s">
+        <v>469</v>
+      </c>
+      <c r="C79" t="s">
+        <v>49</v>
+      </c>
+      <c r="D79" t="s">
+        <v>470</v>
+      </c>
+      <c r="E79" t="s">
+        <v>444</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>38</v>
+      </c>
+      <c r="I79" t="s">
+        <v>61</v>
+      </c>
+      <c r="J79" t="s">
+        <v>38</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>471</v>
+      </c>
+      <c r="M79" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>473</v>
+      </c>
+      <c r="B80" t="s">
+        <v>474</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>475</v>
+      </c>
+      <c r="E80" t="s">
+        <v>476</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>37</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>38</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>477</v>
+      </c>
+      <c r="M80" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>479</v>
+      </c>
+      <c r="B81" t="s">
+        <v>480</v>
+      </c>
+      <c r="C81" t="s">
+        <v>43</v>
+      </c>
+      <c r="D81" t="s">
+        <v>481</v>
+      </c>
+      <c r="E81" t="s">
+        <v>444</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>482</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>38</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>483</v>
+      </c>
+      <c r="M81" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>485</v>
+      </c>
+      <c r="B82" t="s">
+        <v>486</v>
+      </c>
+      <c r="C82" t="s">
+        <v>487</v>
+      </c>
+      <c r="D82" t="s">
+        <v>488</v>
+      </c>
+      <c r="E82" t="s">
+        <v>444</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>390</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s">
+        <v>30</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>489</v>
+      </c>
+      <c r="M82" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>491</v>
+      </c>
+      <c r="B83" t="s">
+        <v>492</v>
+      </c>
+      <c r="C83" t="s">
+        <v>49</v>
+      </c>
+      <c r="D83" t="s">
+        <v>493</v>
+      </c>
+      <c r="E83" t="s">
+        <v>444</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>37</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>38</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>494</v>
+      </c>
+      <c r="M83" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>496</v>
+      </c>
+      <c r="B84" t="s">
+        <v>497</v>
+      </c>
+      <c r="C84" t="s">
+        <v>49</v>
+      </c>
+      <c r="D84" t="s">
+        <v>498</v>
+      </c>
+      <c r="E84" t="s">
+        <v>499</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>38</v>
+      </c>
+      <c r="I84" t="s">
+        <v>61</v>
+      </c>
+      <c r="J84" t="s">
+        <v>38</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>500</v>
+      </c>
+      <c r="M84" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>502</v>
+      </c>
+      <c r="B85" t="s">
+        <v>503</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" t="s">
+        <v>504</v>
+      </c>
+      <c r="E85" t="s">
+        <v>444</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>141</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>22</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>505</v>
+      </c>
+      <c r="M85" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>507</v>
+      </c>
+      <c r="B86" t="s">
+        <v>508</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>509</v>
+      </c>
+      <c r="E86" t="s">
+        <v>444</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>38</v>
+      </c>
+      <c r="I86" t="s">
+        <v>61</v>
+      </c>
+      <c r="J86" t="s">
+        <v>30</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>510</v>
+      </c>
+      <c r="M86" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>512</v>
+      </c>
+      <c r="B87" t="s">
+        <v>513</v>
+      </c>
+      <c r="C87" t="s">
+        <v>219</v>
+      </c>
+      <c r="D87" t="s">
+        <v>514</v>
+      </c>
+      <c r="E87" t="s">
+        <v>461</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>37</v>
+      </c>
+      <c r="I87" t="s">
+        <v>515</v>
+      </c>
+      <c r="J87" t="s">
+        <v>38</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>516</v>
+      </c>
+      <c r="M87" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>518</v>
+      </c>
+      <c r="B88" t="s">
+        <v>519</v>
+      </c>
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" t="s">
+        <v>520</v>
+      </c>
+      <c r="E88" t="s">
+        <v>461</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>37</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>30</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>521</v>
+      </c>
+      <c r="M88" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>523</v>
+      </c>
+      <c r="B89" t="s">
+        <v>524</v>
+      </c>
+      <c r="C89" t="s">
+        <v>239</v>
+      </c>
+      <c r="D89" t="s">
+        <v>525</v>
+      </c>
+      <c r="E89" t="s">
+        <v>526</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>482</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>30</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>527</v>
+      </c>
+      <c r="M89" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>529</v>
+      </c>
+      <c r="B90" t="s">
+        <v>530</v>
+      </c>
+      <c r="C90" t="s">
+        <v>239</v>
+      </c>
+      <c r="D90" t="s">
+        <v>531</v>
+      </c>
+      <c r="E90" t="s">
+        <v>526</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>38</v>
+      </c>
+      <c r="I90" t="s">
+        <v>61</v>
+      </c>
+      <c r="J90" t="s">
+        <v>532</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>533</v>
+      </c>
+      <c r="M90" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>535</v>
+      </c>
+      <c r="B91" t="s">
+        <v>536</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>537</v>
+      </c>
+      <c r="E91" t="s">
+        <v>526</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>37</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>38</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>538</v>
+      </c>
+      <c r="M91" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>540</v>
+      </c>
+      <c r="B92" t="s">
+        <v>541</v>
+      </c>
+      <c r="C92" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>542</v>
+      </c>
+      <c r="E92" t="s">
+        <v>526</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>214</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>30</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>543</v>
+      </c>
+      <c r="M92" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>545</v>
+      </c>
+      <c r="B93" t="s">
+        <v>546</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>547</v>
+      </c>
+      <c r="E93" t="s">
+        <v>526</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>254</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>30</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>548</v>
+      </c>
+      <c r="M93" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>550</v>
+      </c>
+      <c r="B94" t="s">
+        <v>551</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>552</v>
+      </c>
+      <c r="E94" t="s">
+        <v>526</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>372</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>30</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>553</v>
+      </c>
+      <c r="M94" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>555</v>
+      </c>
+      <c r="B95" t="s">
+        <v>556</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>557</v>
+      </c>
+      <c r="E95" t="s">
+        <v>558</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>29</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s">
+        <v>38</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>559</v>
+      </c>
+      <c r="M95" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>561</v>
+      </c>
+      <c r="B96" t="s">
+        <v>562</v>
+      </c>
+      <c r="C96" t="s">
+        <v>239</v>
+      </c>
+      <c r="D96" t="s">
+        <v>563</v>
+      </c>
+      <c r="E96" t="s">
+        <v>526</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>564</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>565</v>
+      </c>
+      <c r="M96" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>567</v>
+      </c>
+      <c r="B97" t="s">
+        <v>568</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" t="s">
+        <v>569</v>
+      </c>
+      <c r="E97" t="s">
+        <v>526</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>38</v>
+      </c>
+      <c r="I97" t="s">
+        <v>61</v>
+      </c>
+      <c r="J97" t="s">
+        <v>38</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>570</v>
+      </c>
+      <c r="M97" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>572</v>
+      </c>
+      <c r="B98" t="s">
+        <v>573</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
+        <v>574</v>
+      </c>
+      <c r="E98" t="s">
+        <v>526</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>37</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>30</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>575</v>
+      </c>
+      <c r="M98" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>577</v>
+      </c>
+      <c r="B99" t="s">
+        <v>578</v>
+      </c>
+      <c r="C99" t="s">
+        <v>35</v>
+      </c>
+      <c r="D99" t="s">
+        <v>579</v>
+      </c>
+      <c r="E99" t="s">
+        <v>526</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>482</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>30</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>580</v>
+      </c>
+      <c r="M99" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>582</v>
+      </c>
+      <c r="B100" t="s">
+        <v>583</v>
+      </c>
+      <c r="C100" t="s">
+        <v>35</v>
+      </c>
+      <c r="D100" t="s">
+        <v>584</v>
+      </c>
+      <c r="E100" t="s">
+        <v>585</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>37</v>
+      </c>
+      <c r="I100" t="s">
+        <v>21</v>
+      </c>
+      <c r="J100" t="s">
+        <v>38</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>586</v>
+      </c>
+      <c r="M100" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>588</v>
+      </c>
+      <c r="B101" t="s">
+        <v>589</v>
+      </c>
+      <c r="C101" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" t="s">
+        <v>590</v>
+      </c>
+      <c r="E101" t="s">
+        <v>591</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>38</v>
+      </c>
+      <c r="I101" t="s">
+        <v>61</v>
+      </c>
+      <c r="J101" t="s">
+        <v>38</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" t="s">
+        <v>592</v>
+      </c>
+      <c r="M101" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>594</v>
+      </c>
+      <c r="B102" t="s">
+        <v>595</v>
+      </c>
+      <c r="C102" t="s">
+        <v>35</v>
+      </c>
+      <c r="D102" t="s">
+        <v>596</v>
+      </c>
+      <c r="E102" t="s">
+        <v>585</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>38</v>
+      </c>
+      <c r="I102" t="s">
+        <v>61</v>
+      </c>
+      <c r="J102" t="s">
+        <v>38</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>597</v>
+      </c>
+      <c r="M102" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>599</v>
+      </c>
+      <c r="B103" t="s">
+        <v>600</v>
+      </c>
+      <c r="C103" t="s">
+        <v>43</v>
+      </c>
+      <c r="D103" t="s">
+        <v>601</v>
+      </c>
+      <c r="E103" t="s">
+        <v>526</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>602</v>
+      </c>
+      <c r="I103" t="s">
+        <v>21</v>
+      </c>
+      <c r="J103" t="s">
+        <v>30</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" t="s">
+        <v>603</v>
+      </c>
+      <c r="M103" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>605</v>
+      </c>
+      <c r="B104" t="s">
+        <v>606</v>
+      </c>
+      <c r="C104" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" t="s">
+        <v>607</v>
+      </c>
+      <c r="E104" t="s">
+        <v>526</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>141</v>
+      </c>
+      <c r="I104" t="s">
+        <v>21</v>
+      </c>
+      <c r="J104" t="s">
+        <v>282</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" t="s">
+        <v>608</v>
+      </c>
+      <c r="M104" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>610</v>
+      </c>
+      <c r="B105" t="s">
+        <v>611</v>
+      </c>
+      <c r="C105" t="s">
+        <v>49</v>
+      </c>
+      <c r="D105" t="s">
+        <v>612</v>
+      </c>
+      <c r="E105" t="s">
+        <v>585</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>38</v>
+      </c>
+      <c r="I105" t="s">
+        <v>61</v>
+      </c>
+      <c r="J105" t="s">
+        <v>38</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" t="s">
+        <v>613</v>
+      </c>
+      <c r="M105" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>615</v>
+      </c>
+      <c r="B106" t="s">
+        <v>616</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" t="s">
+        <v>617</v>
+      </c>
+      <c r="E106" t="s">
+        <v>526</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>37</v>
+      </c>
+      <c r="I106" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s">
+        <v>38</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" t="s">
+        <v>618</v>
+      </c>
+      <c r="M106" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>620</v>
+      </c>
+      <c r="B107" t="s">
+        <v>621</v>
+      </c>
+      <c r="C107" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" t="s">
+        <v>622</v>
+      </c>
+      <c r="E107" t="s">
+        <v>526</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>37</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s">
+        <v>38</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" t="s">
+        <v>623</v>
+      </c>
+      <c r="M107" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>625</v>
+      </c>
+      <c r="B108" t="s">
+        <v>626</v>
+      </c>
+      <c r="C108" t="s">
+        <v>49</v>
+      </c>
+      <c r="D108" t="s">
+        <v>627</v>
+      </c>
+      <c r="E108" t="s">
+        <v>558</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>38</v>
+      </c>
+      <c r="I108" t="s">
+        <v>61</v>
+      </c>
+      <c r="J108" t="s">
+        <v>38</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" t="s">
+        <v>628</v>
+      </c>
+      <c r="M108" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>630</v>
+      </c>
+      <c r="B109" t="s">
+        <v>631</v>
+      </c>
+      <c r="C109" t="s">
+        <v>49</v>
+      </c>
+      <c r="D109" t="s">
+        <v>632</v>
+      </c>
+      <c r="E109" t="s">
+        <v>526</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>38</v>
+      </c>
+      <c r="I109" t="s">
+        <v>61</v>
+      </c>
+      <c r="J109" t="s">
+        <v>38</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" t="s">
+        <v>633</v>
+      </c>
+      <c r="M109" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>635</v>
+      </c>
+      <c r="B110" t="s">
+        <v>636</v>
+      </c>
+      <c r="C110" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" t="s">
+        <v>637</v>
+      </c>
+      <c r="E110" t="s">
+        <v>526</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>390</v>
+      </c>
+      <c r="I110" t="s">
+        <v>21</v>
+      </c>
+      <c r="J110" t="s">
+        <v>38</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" t="s">
+        <v>638</v>
+      </c>
+      <c r="M110" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>640</v>
+      </c>
+      <c r="B111" t="s">
+        <v>641</v>
+      </c>
+      <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" t="s">
+        <v>642</v>
+      </c>
+      <c r="E111" t="s">
+        <v>526</v>
+      </c>
+      <c r="F111" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" t="s">
+        <v>38</v>
+      </c>
+      <c r="I111" t="s">
+        <v>61</v>
+      </c>
+      <c r="J111" t="s">
+        <v>38</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" t="s">
+        <v>643</v>
+      </c>
+      <c r="M111" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>645</v>
+      </c>
+      <c r="B112" t="s">
+        <v>646</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>647</v>
+      </c>
+      <c r="E112" t="s">
+        <v>526</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>102</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>38</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" t="s">
+        <v>648</v>
+      </c>
+      <c r="M112" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>650</v>
+      </c>
+      <c r="B113" t="s">
+        <v>651</v>
+      </c>
+      <c r="C113" t="s">
+        <v>87</v>
+      </c>
+      <c r="D113" t="s">
+        <v>652</v>
+      </c>
+      <c r="E113" t="s">
+        <v>653</v>
+      </c>
+      <c r="F113" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" t="s">
+        <v>37</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s">
+        <v>30</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" t="s">
+        <v>654</v>
+      </c>
+      <c r="M113" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>656</v>
+      </c>
+      <c r="B114" t="s">
+        <v>657</v>
+      </c>
+      <c r="C114" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" t="s">
+        <v>658</v>
+      </c>
+      <c r="E114" t="s">
+        <v>526</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>37</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s">
+        <v>30</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" t="s">
+        <v>659</v>
+      </c>
+      <c r="M114" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>661</v>
+      </c>
+      <c r="B115" t="s">
+        <v>662</v>
+      </c>
+      <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" t="s">
+        <v>663</v>
+      </c>
+      <c r="E115" t="s">
+        <v>664</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>37</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s">
+        <v>22</v>
+      </c>
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" t="s">
+        <v>665</v>
+      </c>
+      <c r="M115" t="s">
+        <v>666</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
